--- a/fhir/ValueSet-dk-ihe-eventcodelists-vs.xlsx
+++ b/fhir/ValueSet-dk-ihe-eventcodelists-vs.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="61">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>9.0.1</t>
+    <t>10.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -184,6 +184,9 @@
   </si>
   <si>
     <t>MCS88021</t>
+  </si>
+  <si>
+    <t>MCS88214</t>
   </si>
   <si>
     <t>urn:oid:1.2.208.184.100.8</t>
@@ -637,7 +640,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -696,18 +699,24 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="B9" t="s" s="2">
-        <v>36</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="B9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
         <v>37</v>
       </c>
-      <c r="B10" t="s" s="2">
-        <v>56</v>
+      <c r="B11" t="s" s="2">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -726,12 +735,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3">
@@ -747,7 +756,7 @@
         <v>37</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/fhir/ValueSet-dk-ihe-eventcodelists-vs.xlsx
+++ b/fhir/ValueSet-dk-ihe-eventcodelists-vs.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.0</t>
+    <t>10.0.1</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/ValueSet-dk-ihe-eventcodelists-vs.xlsx
+++ b/fhir/ValueSet-dk-ihe-eventcodelists-vs.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.1</t>
+    <t>10.0.2</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/ValueSet-dk-ihe-eventcodelists-vs.xlsx
+++ b/fhir/ValueSet-dk-ihe-eventcodelists-vs.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.2</t>
+    <t>11.0.0</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/ValueSet-dk-ihe-eventcodelists-vs.xlsx
+++ b/fhir/ValueSet-dk-ihe-eventcodelists-vs.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.0</t>
+    <t>11.0.1</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/ValueSet-dk-ihe-eventcodelists-vs.xlsx
+++ b/fhir/ValueSet-dk-ihe-eventcodelists-vs.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.1</t>
+    <t>11.0.2</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/ValueSet-dk-ihe-eventcodelists-vs.xlsx
+++ b/fhir/ValueSet-dk-ihe-eventcodelists-vs.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.2</t>
+    <t>11.0.3</t>
   </si>
   <si>
     <t>Name</t>
